--- a/data/trans_orig/P36BPD08_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de vasos de vino que consumen a la semana en 2023</t>
+          <t>Población según el número de vasos de vino que consumen a la semana en 2023 (tasa de respuesta: 99,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>409765</t>
+          <t>410553</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>442785</t>
+          <t>443292</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>423199</t>
+          <t>424947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>436520</t>
+          <t>437039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>841456</t>
+          <t>841937</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>876156</t>
+          <t>877031</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,39%</t>
+          <t>88,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>92,12%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20509</t>
+          <t>20995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>46228</t>
+          <t>44129</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7010</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>17658</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30562</t>
+          <t>30629</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>33921</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>59106</t>
+          <t>57823</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2220</t>
+          <t>2322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9339</t>
+          <t>8901</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39224</t>
+          <t>39207</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>63137</t>
+          <t>64490</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>393544</t>
+          <t>391967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418231</t>
+          <t>418298</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>353067</t>
+          <t>354368</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>368748</t>
+          <t>369640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>754748</t>
+          <t>753878</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>785003</t>
+          <t>783483</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>93,85%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14373</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35401</t>
+          <t>34080</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4687</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13979</t>
+          <t>14099</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21059</t>
+          <t>21527</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>44357</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15650</t>
+          <t>15101</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31782</t>
+          <t>31957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6795</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18611</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25539</t>
+          <t>25504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45745</t>
+          <t>45739</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>561953</t>
+          <t>563344</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646098</t>
+          <t>642806</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>152117</t>
+          <t>151085</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160925</t>
+          <t>160928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>725023</t>
+          <t>725988</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>805525</t>
+          <t>806465</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5032</t>
+          <t>4819</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33302</t>
+          <t>33094</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2375</t>
+          <t>2308</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>8872</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8282</t>
+          <t>7805</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36473</t>
+          <t>36023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14024</t>
+          <t>16364</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>76440</t>
+          <t>75191</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9112</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>16757</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76863</t>
+          <t>75843</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>856830</t>
+          <t>853179</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>904875</t>
+          <t>903678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>945534</t>
+          <t>945995</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>967144</t>
+          <t>966766</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1806206</t>
+          <t>1806463</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1897054</t>
+          <t>1887634</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>93,9%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41636</t>
+          <t>41001</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83369</t>
+          <t>80874</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20237</t>
+          <t>20610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47393</t>
+          <t>47629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98823</t>
+          <t>96073</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>78632</t>
+          <t>77634</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>111847</t>
+          <t>112274</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3467</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14216</t>
+          <t>13307</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68636</t>
+          <t>68280</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122606</t>
+          <t>122357</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>387883</t>
+          <t>387057</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>417377</t>
+          <t>418244</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>81,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>808291</t>
+          <t>808641</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>826322</t>
+          <t>826171</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1201297</t>
+          <t>1201566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1242077</t>
+          <t>1241338</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,49%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15112</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33460</t>
+          <t>33378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>7023</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18864</t>
+          <t>18980</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48051</t>
+          <t>48534</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34205</t>
+          <t>33027</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59349</t>
+          <t>59861</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>6043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2835,7 +2835,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42968</t>
+          <t>42141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>72812</t>
+          <t>73132</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>217863</t>
+          <t>219323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>236209</t>
+          <t>236158</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>730101</t>
+          <t>728900</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>745009</t>
+          <t>744743</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>956002</t>
+          <t>955283</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>977960</t>
+          <t>977362</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>19632</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3138,12 +3138,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16332</t>
+          <t>16629</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3173,12 +3173,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3193,12 +3193,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>11524</t>
+          <t>11596</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3208,12 +3208,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3111</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7226</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>18364</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19996</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2908480</t>
+          <t>2908767</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3056529</t>
+          <t>3048199</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3441649</t>
+          <t>3443095</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3484883</t>
+          <t>3485320</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6363359</t>
+          <t>6364893</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6495493</t>
+          <t>6496352</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,54%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>118170</t>
+          <t>121993</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>194863</t>
+          <t>190178</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47045</t>
+          <t>47893</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>74031</t>
+          <t>75956</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>180918</t>
+          <t>181155</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>253753</t>
+          <t>256630</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>195034</t>
+          <t>202536</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>284724</t>
+          <t>287862</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>40366</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>67997</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>264062</t>
+          <t>259142</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>345574</t>
+          <t>342212</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD08_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD08_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>428636</t>
+          <t>468225</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>410553</t>
+          <t>450323</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>443292</t>
+          <t>483536</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>431536</t>
+          <t>469685</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>424947</t>
+          <t>461356</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>437039</t>
+          <t>475927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>860172</t>
+          <t>937909</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>841937</t>
+          <t>916892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>877031</t>
+          <t>954806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,96%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30431</t>
+          <t>31814</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20995</t>
+          <t>22613</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>44129</t>
+          <t>46422</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11305</t>
+          <t>12743</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17658</t>
+          <t>20371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>41736</t>
+          <t>44557</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>33498</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>58265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>45471</t>
+          <t>49851</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>33921</t>
+          <t>38734</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>57823</t>
+          <t>63894</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,22 +986,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>5983</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8901</t>
+          <t>11155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>50096</t>
+          <t>55835</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>39207</t>
+          <t>43013</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>70530</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>504538</t>
+          <t>549890</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>504538</t>
+          <t>549890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>504538</t>
+          <t>549890</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>952005</t>
+          <t>1038301</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>952005</t>
+          <t>1038301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>952005</t>
+          <t>1038301</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>407251</t>
+          <t>433224</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>391967</t>
+          <t>417360</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>418298</t>
+          <t>444920</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,68%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>362810</t>
+          <t>400446</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>354368</t>
+          <t>391081</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>369640</t>
+          <t>407143</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>770062</t>
+          <t>833669</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>753878</t>
+          <t>814472</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>783483</t>
+          <t>848782</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22094</t>
+          <t>22581</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13820</t>
+          <t>14541</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34080</t>
+          <t>35438</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>9759</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4687</t>
+          <t>5789</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>16305</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>30374</t>
+          <t>32339</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21527</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>44357</t>
+          <t>44881</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22867</t>
+          <t>27408</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>18268</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31957</t>
+          <t>37700</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11490</t>
+          <t>12939</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6193</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18126</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>34357</t>
+          <t>40346</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>25504</t>
+          <t>31148</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>45739</t>
+          <t>54635</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>605698</t>
+          <t>404079</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>563344</t>
+          <t>389211</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642806</t>
+          <t>418193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>82,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>88,9%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>156993</t>
+          <t>176606</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>151085</t>
+          <t>170768</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>160928</t>
+          <t>181051</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>762691</t>
+          <t>580685</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>725988</t>
+          <t>563989</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>806465</t>
+          <t>596183</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>87,05%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>90,61%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4819</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33094</t>
+          <t>29617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4874</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2308</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8872</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>23577</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7805</t>
+          <t>15096</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36023</t>
+          <t>34855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>44413</t>
+          <t>48157</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16364</t>
+          <t>36551</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>75191</t>
+          <t>60495</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>10,24%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2380</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9676</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>49457</t>
+          <t>53669</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>16757</t>
+          <t>42473</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75843</t>
+          <t>68113</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>10,35%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>667057</t>
+          <t>470434</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>667057</t>
+          <t>470434</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>667057</t>
+          <t>470434</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>833967</t>
+          <t>657931</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>833967</t>
+          <t>657931</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833967</t>
+          <t>657931</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>883144</t>
+          <t>969883</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>853179</t>
+          <t>941966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>903678</t>
+          <t>993077</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>955845</t>
+          <t>833847</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>945995</t>
+          <t>823861</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>966766</t>
+          <t>841870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1838989</t>
+          <t>1803730</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1806463</t>
+          <t>1776045</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1887634</t>
+          <t>1829039</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>91,94%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>57186</t>
+          <t>58194</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>41001</t>
+          <t>42505</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80874</t>
+          <t>79736</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>15112</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6228</t>
+          <t>9491</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20610</t>
+          <t>23219</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>73306</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47629</t>
+          <t>57132</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>96073</t>
+          <t>97531</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>93006</t>
+          <t>101316</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>77634</t>
+          <t>84378</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>112274</t>
+          <t>119903</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8070</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>6279</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13307</t>
+          <t>19182</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>101076</t>
+          <t>112410</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>68280</t>
+          <t>94952</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>122357</t>
+          <t>132384</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1033335</t>
+          <t>1129393</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033335</t>
+          <t>1129393</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1033335</t>
+          <t>1129393</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>976938</t>
+          <t>860053</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>976938</t>
+          <t>860053</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>976938</t>
+          <t>860053</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2010273</t>
+          <t>1989446</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2010273</t>
+          <t>1989446</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2010273</t>
+          <t>1989446</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>403465</t>
+          <t>489799</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>387057</t>
+          <t>470728</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>418244</t>
+          <t>505149</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>88,54%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>818640</t>
+          <t>806050</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>808641</t>
+          <t>797022</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>826171</t>
+          <t>813692</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1222105</t>
+          <t>1295849</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1201566</t>
+          <t>1274829</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1241338</t>
+          <t>1313282</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,07%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22823</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>15246</t>
+          <t>16127</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33378</t>
+          <t>36359</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>11723</t>
+          <t>13058</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7023</t>
+          <t>8013</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18980</t>
+          <t>20284</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>34545</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>27189</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>48534</t>
+          <t>50429</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,61%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>46067</t>
+          <t>51061</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33027</t>
+          <t>38876</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59861</t>
+          <t>67008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>10973</t>
+          <t>11742</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6043</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17652</t>
+          <t>18433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>57039</t>
+          <t>62802</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73132</t>
+          <t>80936</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>472355</t>
+          <t>565162</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>472355</t>
+          <t>565162</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>472355</t>
+          <t>565162</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1313690</t>
+          <t>1396012</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313690</t>
+          <t>1396012</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1313690</t>
+          <t>1396012</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,32 +3005,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>230279</t>
+          <t>226372</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>219323</t>
+          <t>215623</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>236158</t>
+          <t>232611</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>738073</t>
+          <t>819073</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>728900</t>
+          <t>810060</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>744743</t>
+          <t>826334</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>968352</t>
+          <t>1045445</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>955283</t>
+          <t>1031985</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>977362</t>
+          <t>1055357</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -3118,102 +3118,102 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>8705</t>
+          <t>9206</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>3112</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19632</t>
+          <t>20249</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8,58%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>11281</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>6587</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>16685</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>20487</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>12800</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>32295</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
           <t>1,19%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8,2%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>10606</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>6251</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>16629</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>19311</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>11596</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>30042</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>1,93%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3241,12 +3241,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>12150</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7930</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>20960</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>12671</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>760830</t>
+          <t>843678</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>760830</t>
+          <t>843678</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>760830</t>
+          <t>843678</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1000334</t>
+          <t>1079764</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1000334</t>
+          <t>1079764</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1000334</t>
+          <t>1079764</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>2958472</t>
+          <t>2991582</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2908767</t>
+          <t>2947658</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3048199</t>
+          <t>3032439</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3463899</t>
+          <t>3505706</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3443095</t>
+          <t>3486432</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3485320</t>
+          <t>3523641</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6422372</t>
+          <t>6497288</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>6364893</t>
+          <t>6447700</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6496352</t>
+          <t>6541001</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>92,55%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>158184</t>
+          <t>164294</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121993</t>
+          <t>136716</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>190178</t>
+          <t>195384</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>59810</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>47893</t>
+          <t>55461</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>82181</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>217994</t>
+          <t>231627</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>181155</t>
+          <t>204371</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>256630</t>
+          <t>265078</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>252345</t>
+          <t>278301</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>202536</t>
+          <t>250407</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>287862</t>
+          <t>312134</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>52353</t>
+          <t>60593</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>48387</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>67997</t>
+          <t>76663</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>304697</t>
+          <t>338894</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>259142</t>
+          <t>307700</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>342212</t>
+          <t>375657</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>3369001</t>
+          <t>3434176</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3369001</t>
+          <t>3434176</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3369001</t>
+          <t>3434176</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>3576062</t>
+          <t>3633632</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3576062</t>
+          <t>3633632</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>3576062</t>
+          <t>3633632</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>6945063</t>
+          <t>7067808</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>6945063</t>
+          <t>7067808</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>6945063</t>
+          <t>7067808</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
